--- a/sheets/대금율보/검수/유리벽 사랑.xlsx
+++ b/sheets/대금율보/검수/유리벽 사랑.xlsx
@@ -3807,14 +3807,14 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹汰</t>
         </is>
       </c>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –太</t>
         </is>
       </c>
@@ -4008,14 +4008,14 @@
       <c r="G9" s="23"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南‹
+          <t xml:space="preserve">南
 –太</t>
         </is>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K9" s="23"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹‹
+          <t xml:space="preserve">浹
 淋</t>
         </is>
       </c>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 浹</t>
         </is>
       </c>
@@ -4450,7 +4450,7 @@
       <c r="E20" s="23"/>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–林‹
+          <t xml:space="preserve">–林
 夾</t>
         </is>
       </c>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–無‹
+          <t xml:space="preserve">–無
 南</t>
         </is>
       </c>
@@ -4487,7 +4487,7 @@
       <c r="F21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太太
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">

--- a/sheets/대금율보/검수/유리벽 사랑.xlsx
+++ b/sheets/대금율보/검수/유리벽 사랑.xlsx
@@ -3700,22 +3700,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.84" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.84" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="K18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="K20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.84" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.84" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -4553,6 +4553,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>